--- a/staff_forms/003_work_satisfaction_survey--staff_forms.xlsx
+++ b/staff_forms/003_work_satisfaction_survey--staff_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -727,8 +727,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -756,12 +756,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'too_much_work'}</t>
+          <t>too_much_work</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Too much work'}</t>
+          <t>Too much work</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'just_right'}</t>
+          <t>just_right</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Just right'}</t>
+          <t>Just right</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_enough_work'}</t>
+          <t>not_enough_work</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not enough work'}</t>
+          <t>Not enough work</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'too_much_responsibility'}</t>
+          <t>too_much_responsibility</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Too much responsibility'}</t>
+          <t>Too much responsibility</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'just_right'}</t>
+          <t>just_right</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Just right'}</t>
+          <t>Just right</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'not_enough_responsibility'}</t>
+          <t>not_enough_responsibility</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Not enough responsibility'}</t>
+          <t>Not enough responsibility</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
